--- a/Experiments/EX-C2/EX-C2a/EX-C2a-homo_log_vgg16.xlsx
+++ b/Experiments/EX-C2/EX-C2a/EX-C2a-homo_log_vgg16.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Model IP Protection\locking model scheme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Model IP Protection\ChannelCrypt\Experiments\EX-C2\EX-C2a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03F4750-5801-4DF2-8646-BBEE9E77200F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75166D7-CAC5-4F4A-A5AE-8EFDD6D7597E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1212" yWindow="3048" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,6 @@
     <t>Metric</t>
   </si>
   <si>
-    <t>VGG16 on CIFAR-10</t>
-  </si>
-  <si>
-    <t>VGG16 on CIFAR-100</t>
-  </si>
-  <si>
-    <t>VGG16 on ImageNet</t>
-  </si>
-  <si>
     <t>Layer4.0.Conv2d</t>
   </si>
   <si>
@@ -120,6 +111,18 @@
       </rPr>
       <t>↑</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResNet18 on CIFAR-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResNet18 on CIFAR-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResNet18 on ImageNet</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -547,19 +550,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -568,64 +571,64 @@
     <row r="2" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>0</v>
@@ -633,7 +636,7 @@
     </row>
     <row r="4" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3">
         <v>0.83919999999999995</v>
@@ -674,7 +677,7 @@
     </row>
     <row r="5" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3">
         <v>0.62509999999999999</v>
@@ -715,7 +718,7 @@
     </row>
     <row r="6" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
         <v>0.68240000000000001</v>
@@ -756,7 +759,7 @@
     </row>
     <row r="7" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
         <v>0.63919999999999999</v>
@@ -797,7 +800,7 @@
     </row>
     <row r="8" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>0.61040000000000005</v>
@@ -838,6 +841,7 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:A3"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
@@ -847,7 +851,6 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
